--- a/inquiry_forms/002_flight_details_inquiry_form--inquiry_forms.xlsx
+++ b/inquiry_forms/002_flight_details_inquiry_form--inquiry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,86 +515,86 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>flight_details</t>
+          <t>flight_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Flight Details</t>
+          <t>What type of flight is this?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>passenger_details</t>
+          <t>travel_dates</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Passenger Details</t>
+          <t>When were you planning to travel?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>travel_dates</t>
+          <t>number_of_travelers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Travel Dates</t>
+          <t>How many travelers?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>flight_numbers</t>
+          <t>passenger_details</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Flight Numbers</t>
+          <t>Passenger Names and IDs</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,23 +607,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>flight_numbers</t>
+          <t>special_requests</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Flight Numbers</t>
+          <t>Are there any special requests?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Flight Numbers</t>
+          <t>Which flight numbers do you have?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,40 +653,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>flight_numbers</t>
+          <t>seats_needed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Flight Numbers</t>
+          <t>How many seats do you need?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>flight_numbers</t>
+          <t>travel_class</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Flight Numbers</t>
+          <t>What is the travel class?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,44 +699,90 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>flight_numbers</t>
+          <t>boarding_assistance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Flight Numbers</t>
+          <t>Do you need assistance with boarding?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>flight_numbers</t>
+          <t>special_requirements</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Flight Numbers</t>
+          <t>Do you have any special requirements?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>flight_details</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Add any flight details</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>confirmation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -753,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,34 +827,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>flight_numbers_choices</t>
+          <t>flight_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flight_number</t>
+          <t>flight</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Flight Number</t>
+          <t>Flight</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>flight_numbers_choices</t>
+          <t>flight_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>alternate_flight_number</t>
+          <t>non-flight_(e.g._train,_bus)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alternate Flight Number</t>
+          <t>Non-flight (e.g. train, bus)</t>
         </is>
       </c>
     </row>
@@ -820,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>flight_number</t>
+          <t>flight_number_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Flight Number</t>
+          <t>Flight Number 1</t>
         </is>
       </c>
     </row>
@@ -837,182 +883,63 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>alternate_flight_number</t>
+          <t>alternate_flight_number_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alternate Flight Number</t>
+          <t>Alternate Flight Number 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>flight_numbers_choices</t>
+          <t>travel_class_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>flight_number</t>
+          <t>economy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Flight Number</t>
+          <t>Economy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>flight_numbers_choices</t>
+          <t>travel_class_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>alternate_flight_number</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alternate Flight Number</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>flight_numbers_choices</t>
+          <t>travel_class_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>flight_number</t>
+          <t>first_class</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Flight Number</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>flight_numbers_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>alternate_flight_number</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Alternate Flight Number</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>flight_numbers_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>flight_number</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Flight Number</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>flight_numbers_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>alternate_flight_number</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Alternate Flight Number</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>flight_numbers_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>flight_number</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Flight Number</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>flight_numbers_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>alternate_flight_number</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Alternate Flight Number</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>flight_numbers_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>flight_number</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Flight Number</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>flight_numbers_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>alternate_flight_number</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Alternate Flight Number</t>
+          <t>First Class</t>
         </is>
       </c>
     </row>
